--- a/data/trending_integrated_20261026_14.xlsx
+++ b/data/trending_integrated_20261026_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59023389505</v>
+        <v>59027708365</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.51%</t>
+          <t>'+7.25%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>66735240179</v>
+        <v>66951276919</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -762,13 +762,13 @@
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F4" t="n">
         <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>41822383075</v>
+        <v>41977700015</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G5" t="n">
-        <v>1853</v>
+        <v>1821</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2206622156500</v>
+        <v>2300287736500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물린 주가 하락에 대한 불만 표출. 과거 급등락 경험 언급.</t>
+          <t>주가 하락에 대한 불만과 정치적 이슈에 대한 부정적 언급. 일부 긍정적 전망도 있으나 근거 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인', '주가']</t>
+          <t>['주가 하락', '외인 매매', '전망']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60500</v>
+        <v>60300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.17%</t>
+          <t>'+0.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G6" t="n">
-        <v>835</v>
+        <v>873</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -969,7 +969,7 @@
         <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>60600</v>
+        <v>60700</v>
       </c>
       <c r="M6" t="n">
         <v>57700</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>251681475750</v>
+        <v>260526852250</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>향후 호재에 대한 기대감과 기술적 분석 기반 긍정적 전망. 외인 매수세 언급.</t>
+          <t>기술적 분석과 수급 동향을 기반으로 긍정적인 전망 제시. 공매도 세력에 대한 언급 포함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급동향']</t>
+          <t>['기술적 분석', '수급 동향', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215250</v>
+        <v>214500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G7" t="n">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1699345492750</v>
+        <v>1747184581250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 부정적 언급과 시장 불만 표출. 외인 매도세 언급.</t>
+          <t>종목의 펀더멘털 분석이나 전망에 대한 내용은 부재함. 정치적 이슈에 대한 부정적 언급이 다수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58200</v>
+        <v>58000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G8" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>60638967600</v>
+        <v>61779444500</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16450</v>
+        <v>16420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>25357152160</v>
+        <v>26023949095</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14280</v>
+        <v>14250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>20392340240</v>
+        <v>20600810070</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26900</v>
+        <v>26850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-5.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>44713654525</v>
+        <v>46375580200</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3105</v>
+        <v>3085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-18.50%</t>
+          <t>'-19.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F12" t="n">
         <v>140</v>
       </c>
       <c r="G12" t="n">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24799045732</v>
+        <v>25061867638</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_14.xlsx
+++ b/data/trending_integrated_20261026_14.xlsx
@@ -584,7 +584,7 @@
         <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59027708365</v>
+        <v>59040958745</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -622,7 +622,7 @@
         <v>336000</v>
       </c>
       <c r="S2" t="n">
-        <v>307000</v>
+        <v>306000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2085</v>
+        <v>2105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.25%</t>
+          <t>'+8.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>66951276919</v>
+        <v>67307574031</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -711,7 +711,7 @@
         <v>749</v>
       </c>
       <c r="R3" t="n">
-        <v>-27000</v>
+        <v>-106000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>41977700015</v>
+        <v>42210539875</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -803,7 +803,7 @@
         <v>3660</v>
       </c>
       <c r="R4" t="n">
-        <v>-45000</v>
+        <v>-46000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="G5" t="n">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2300287736500</v>
+        <v>2376924758000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,14 +895,14 @@
         <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>-134000</v>
+        <v>-161000</v>
       </c>
       <c r="S5" t="n">
-        <v>77000</v>
+        <v>122000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 정치적 이슈에 대한 부정적 언급. 일부 긍정적 전망도 있으나 근거 부족.</t>
+          <t>정치적 발언과 함께 주가 하락에 대한 우려 표출. 외인 매매 동향 및 과거 주가 변동성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 하락', '외인 매매', '전망']</t>
+          <t>['외인', '주가', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60300</v>
+        <v>60600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.84%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>873</v>
+        <v>951</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -969,7 +969,7 @@
         <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>60700</v>
+        <v>60800</v>
       </c>
       <c r="M6" t="n">
         <v>57700</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>260526852250</v>
+        <v>269946709500</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -987,23 +987,23 @@
         <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>396000</v>
+        <v>558000</v>
       </c>
       <c r="S6" t="n">
-        <v>65000</v>
+        <v>87000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>기술적 분석과 수급 동향을 기반으로 긍정적인 전망 제시. 공매도 세력에 대한 언급 포함.</t>
+          <t>실적 개선 기대감과 공매도 세력과의 수급 싸움 분석. 숏커버링 및 유동성 장세 진입 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급 동향', '공매도']</t>
+          <t>['실적', '공매도', '수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214500</v>
+        <v>215000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1747184581250</v>
+        <v>1807330074500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,14 +1079,14 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-859000</v>
+        <v>-882000</v>
       </c>
       <c r="S7" t="n">
-        <v>-5000</v>
+        <v>220000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>종목의 펀더멘털 분석이나 전망에 대한 내용은 부재함. 정치적 이슈에 대한 부정적 언급이 다수.</t>
+          <t>정치적 발언과 개인적인 감정 표출이 주를 이루며, 주가 관련 객관적 근거 부재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58000</v>
+        <v>16410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>566</v>
+        <v>235</v>
       </c>
       <c r="H8" t="n">
-        <v>22.23</v>
+        <v>27.94</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59400</v>
+        <v>16830</v>
       </c>
       <c r="K8" t="n">
-        <v>58300</v>
+        <v>16520</v>
       </c>
       <c r="L8" t="n">
-        <v>59100</v>
+        <v>16820</v>
       </c>
       <c r="M8" t="n">
-        <v>57200</v>
+        <v>16340</v>
       </c>
       <c r="N8" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>61779444500</v>
+        <v>26721327155</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>16340</v>
       </c>
       <c r="R8" t="n">
-        <v>-82000</v>
+        <v>414000</v>
       </c>
       <c r="S8" t="n">
-        <v>-122000</v>
+        <v>-110000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성 언급에도 불구하고, 정부 정책 및 증시 전반에 대한 부정적 인식.</t>
+          <t>국내 조선업의 경쟁력 약화와 관련된 부정적 뉴스 언급. 주가 하락 및 상장 폐지 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전 수주', '정부 정책', '증시 붕괴']</t>
+          <t>['조선', '수주', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16420</v>
+        <v>57900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="G9" t="n">
-        <v>232</v>
+        <v>578</v>
       </c>
       <c r="H9" t="n">
-        <v>27.94</v>
+        <v>22.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16830</v>
+        <v>59400</v>
       </c>
       <c r="K9" t="n">
-        <v>16520</v>
+        <v>58300</v>
       </c>
       <c r="L9" t="n">
-        <v>16820</v>
+        <v>59100</v>
       </c>
       <c r="M9" t="n">
-        <v>16340</v>
+        <v>57200</v>
       </c>
       <c r="N9" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>26023949095</v>
+        <v>62967225000</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>16340</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>349000</v>
+        <v>-72000</v>
       </c>
       <c r="S9" t="n">
-        <v>-60000</v>
+        <v>-151000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내 조선업의 경쟁력 약화와 관련된 부정적 뉴스 언급. 주가 하락 및 상장 폐지 우려.</t>
+          <t>폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성 언급에도 불구하고, 정부 정책 및 증시 전반에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['조선', '수주', '실적']</t>
+          <t>['원전 수주', '정부 정책', '증시 붕괴']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14250</v>
+        <v>14270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>20600810070</v>
+        <v>21025302625</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,7 +1355,7 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>68000</v>
+        <v>98000</v>
       </c>
       <c r="S10" t="n">
         <v>-17000</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26850</v>
+        <v>26650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.62%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1432,13 +1432,13 @@
         <v>28200</v>
       </c>
       <c r="M11" t="n">
-        <v>26750</v>
+        <v>26650</v>
       </c>
       <c r="N11" t="n">
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>46375580200</v>
+        <v>48639098350</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1447,10 +1447,10 @@
         <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>-243000</v>
+        <v>-241000</v>
       </c>
       <c r="S11" t="n">
-        <v>-85000</v>
+        <v>-110000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25061867638</v>
+        <v>25317005128</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1539,14 +1539,14 @@
         <v>2500</v>
       </c>
       <c r="R12" t="n">
-        <v>120000</v>
+        <v>69000</v>
       </c>
       <c r="S12" t="n">
         <v>-142000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>북한 관련 테마주 논의 및 주가 급락에 대한 부정적 반응. 루머 및 감정적 표현 위주로, 객관적 근거 제시 부족. 테마주 투자 위험성 암시.</t>
+          <t>테마주 관련 언급과 함께 급격한 주가 하락에 대한 부정적 전망. 시세 조종 및 투자 주의 촉구.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['북한', '테마주', '급락']</t>
+          <t>['테마주', '급락', '시세조종']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_14.xlsx
+++ b/data/trending_integrated_20261026_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G2" t="n">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59040958745</v>
+        <v>59053019235</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 후기 임상 진입 소식 기반. 공매도 스퀴즈 및 리레이팅 기대.</t>
+          <t>AI 신약 개발 관련 빅파마 협력 및 임상 진입 긍정적 전망. 공매도 쇼트커버링 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '빅파마', '공매도 스퀴즈']</t>
+          <t>['AI 신약', '임상', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2105</v>
+        <v>2095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.28%</t>
+          <t>'+7.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>67307574031</v>
+        <v>67508385886</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -762,13 +762,13 @@
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F4" t="n">
         <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>42210539875</v>
+        <v>42313636725</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급과 함께 주가 상승에 대한 기대감 표출. 일부 부정적 언급 존재.</t>
+          <t>정치 테마주 관련 언급 다수. 긍정적 전망 있으나 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마', '우상향', '물려있습니다']</t>
+          <t>['정치 테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1302000</v>
+        <v>1295000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.96%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G5" t="n">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2376924758000</v>
+        <v>2422123611000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -946,13 +946,13 @@
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G6" t="n">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>269946709500</v>
+        <v>276440222150</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 개선 기대감과 공매도 세력과의 수급 싸움 분석. 숏커버링 및 유동성 장세 진입 가능성 언급.</t>
+          <t>실적 개선 및 전망 호조, 공매도 감소 가능성 언급. 긍정적 수급 동향 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215000</v>
+        <v>214250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G7" t="n">
-        <v>1876</v>
+        <v>1911</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1807330074500</v>
+        <v>1850611832500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16410</v>
+        <v>16440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.50%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
         <v>235</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>26721327155</v>
+        <v>27380272325</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>58000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
         <v>137</v>
       </c>
       <c r="G9" t="n">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>62967225000</v>
+        <v>64413281350</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14270</v>
+        <v>14310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.93%</t>
+          <t>'-2.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>21025302625</v>
+        <v>21450236515</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1432,13 +1432,13 @@
         <v>28200</v>
       </c>
       <c r="M11" t="n">
-        <v>26650</v>
+        <v>26550</v>
       </c>
       <c r="N11" t="n">
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>48639098350</v>
+        <v>50559939375</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3085</v>
+        <v>3095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.03%</t>
+          <t>'-18.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F12" t="n">
         <v>141</v>
       </c>
       <c r="G12" t="n">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25317005128</v>
+        <v>25379479004</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>테마주 관련 언급과 함께 급격한 주가 하락에 대한 부정적 전망. 시세 조종 및 투자 주의 촉구.</t>
+          <t>지정학적 리스크 테마주 언급. 급락 및 부정적 전망 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테마주', '급락', '시세조종']</t>
+          <t>['지정학적 리스크']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_14.xlsx
+++ b/data/trending_integrated_20261026_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59053019235</v>
+        <v>59062538355</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -670,13 +670,13 @@
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>67508385886</v>
+        <v>67886670231</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5630</v>
+        <v>5590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+1.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F4" t="n">
         <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>42313636725</v>
+        <v>42504112105</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1295000</v>
+        <v>60700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>1.49</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>194</v>
       </c>
       <c r="F5" t="n">
-        <v>449</v>
+        <v>108</v>
       </c>
       <c r="G5" t="n">
-        <v>1824</v>
+        <v>1008</v>
       </c>
       <c r="H5" t="n">
-        <v>48.69</v>
+        <v>40.39</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1277000</v>
+        <v>59800</v>
       </c>
       <c r="K5" t="n">
-        <v>1279000</v>
+        <v>59400</v>
       </c>
       <c r="L5" t="n">
-        <v>1315000</v>
+        <v>60900</v>
       </c>
       <c r="M5" t="n">
-        <v>1267000</v>
+        <v>57700</v>
       </c>
       <c r="N5" t="n">
-        <v>48.77</v>
+        <v>38.9</v>
       </c>
       <c r="O5" t="n">
-        <v>2422123611000</v>
+        <v>286187211150</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>67300</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>23150</v>
       </c>
       <c r="R5" t="n">
-        <v>-161000</v>
+        <v>558000</v>
       </c>
       <c r="S5" t="n">
-        <v>122000</v>
+        <v>87000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 주가 하락에 대한 우려 표출. 외인 매매 동향 및 과거 주가 변동성 언급.</t>
+          <t>실적 호조와 7000억 매입, 주식 소각 등에 대한 언급이 있으며, 공매도 세력의 손실 및 숏커버링 가능성을 근거로 긍정적인 전망을 제시함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인', '주가', '변동성']</t>
+          <t>['실적', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60600</v>
+        <v>1289000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.49</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>187</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>103</v>
+        <v>453</v>
       </c>
       <c r="G6" t="n">
-        <v>978</v>
+        <v>1812</v>
       </c>
       <c r="H6" t="n">
-        <v>40.39</v>
+        <v>48.69</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>59800</v>
+        <v>1277000</v>
       </c>
       <c r="K6" t="n">
-        <v>59400</v>
+        <v>1279000</v>
       </c>
       <c r="L6" t="n">
-        <v>60800</v>
+        <v>1315000</v>
       </c>
       <c r="M6" t="n">
-        <v>57700</v>
+        <v>1267000</v>
       </c>
       <c r="N6" t="n">
-        <v>38.9</v>
+        <v>48.77</v>
       </c>
       <c r="O6" t="n">
-        <v>276440222150</v>
+        <v>2489720313000</v>
       </c>
       <c r="P6" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>23150</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>558000</v>
+        <v>-161000</v>
       </c>
       <c r="S6" t="n">
-        <v>87000</v>
+        <v>122000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 개선 및 전망 호조, 공매도 감소 가능성 언급. 긍정적 수급 동향 기대.</t>
+          <t>정치적 언급이 다수 포함되었으며, 주가 하락에 대한 부정적 정서와 함께 외인 복귀에 대한 기대가 일부 있으나 명확한 근거는 부족함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '수급']</t>
+          <t>['외인', '주가 하락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G7" t="n">
-        <v>1911</v>
+        <v>1904</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1850611832500</v>
+        <v>1887454824500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 발언과 개인적인 감정 표출이 주를 이루며, 주가 관련 객관적 근거 부재.</t>
+          <t>대부분의 게시글이 특정 정치인 및 정부 정책에 대한 부정적인 감정을 표출하며, 주가에 대한 구체적인 근거 제시가 부족함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1130,13 +1130,13 @@
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>27380272325</v>
+        <v>27937793325</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G9" t="n">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>64413281350</v>
+        <v>66115236350</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성 언급에도 불구하고, 정부 정책 및 증시 전반에 대한 부정적 인식.</t>
+          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전 수주', '정부 정책', '증시 붕괴']</t>
+          <t>['원전', '정치적 요인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14310</v>
+        <v>14350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.65%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>21450236515</v>
+        <v>21987476550</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>50559939375</v>
+        <v>52136287075</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G12" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25379479004</v>
+        <v>25504626411</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_14.xlsx
+++ b/data/trending_integrated_20261026_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>59062538355</v>
+        <v>59069060715</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.77%</t>
+          <t>'+7.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>67886670231</v>
+        <v>68195309134</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5590</v>
+        <v>5580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.82%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>147</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>42504112105</v>
+        <v>42732618255</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급 다수. 긍정적 전망 있으나 명확한 근거 부족.</t>
+          <t>정치 테마주 관련 언급과 함께 주가 상승에 대한 기대감 표출. 일부 부정적 언급 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주']</t>
+          <t>['정치 테마', '우상향', '물려있습니다']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60700</v>
+        <v>1292000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.49</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>194</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>108</v>
+        <v>449</v>
       </c>
       <c r="G5" t="n">
-        <v>1008</v>
+        <v>1851</v>
       </c>
       <c r="H5" t="n">
-        <v>40.39</v>
+        <v>48.69</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>59800</v>
+        <v>1277000</v>
       </c>
       <c r="K5" t="n">
-        <v>59400</v>
+        <v>1279000</v>
       </c>
       <c r="L5" t="n">
-        <v>60900</v>
+        <v>1315000</v>
       </c>
       <c r="M5" t="n">
-        <v>57700</v>
+        <v>1267000</v>
       </c>
       <c r="N5" t="n">
-        <v>38.9</v>
+        <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>286187211150</v>
+        <v>2543660364500</v>
       </c>
       <c r="P5" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>23150</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>558000</v>
+        <v>-161000</v>
       </c>
       <c r="S5" t="n">
-        <v>87000</v>
+        <v>122000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 호조와 7000억 매입, 주식 소각 등에 대한 언급이 있으며, 공매도 세력의 손실 및 숏커버링 가능성을 근거로 긍정적인 전망을 제시함.</t>
+          <t>정치 관련 부정적 언급 다수. 일부 긍정적 전망 및 외인 복귀 기대 있으나 근거 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '숏커버링']</t>
+          <t>['외인', '정치']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1289000</v>
+        <v>60300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>206</v>
       </c>
       <c r="F6" t="n">
-        <v>453</v>
+        <v>116</v>
       </c>
       <c r="G6" t="n">
-        <v>1812</v>
+        <v>1042</v>
       </c>
       <c r="H6" t="n">
-        <v>48.69</v>
+        <v>40.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1277000</v>
+        <v>59800</v>
       </c>
       <c r="K6" t="n">
-        <v>1279000</v>
+        <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>1315000</v>
+        <v>60900</v>
       </c>
       <c r="M6" t="n">
-        <v>1267000</v>
+        <v>57700</v>
       </c>
       <c r="N6" t="n">
-        <v>48.77</v>
+        <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2489720313000</v>
+        <v>295347408050</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>67300</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>-161000</v>
+        <v>558000</v>
       </c>
       <c r="S6" t="n">
-        <v>122000</v>
+        <v>87000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 언급이 다수 포함되었으며, 주가 하락에 대한 부정적 정서와 함께 외인 복귀에 대한 기대가 일부 있으나 명확한 근거는 부족함.</t>
+          <t>실적 호조 및 주식 소각 언급. 공매도 관련 분석 및 수급 기대감. 거래량 동반한 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '주가 하락']</t>
+          <t>['실적', '공매도', '수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214250</v>
+        <v>214500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G7" t="n">
-        <v>1904</v>
+        <v>1886</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1887454824500</v>
+        <v>1919013477250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대부분의 게시글이 특정 정치인 및 정부 정책에 대한 부정적인 감정을 표출하며, 주가에 대한 구체적인 근거 제시가 부족함.</t>
+          <t>정치 관련 언급만 다수. 주가 관련 객관적 근거 없음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16440</v>
+        <v>16420</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>27937793325</v>
+        <v>28576780565</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58000</v>
+        <v>57800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F9" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G9" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>66115236350</v>
+        <v>67986515150</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14350</v>
+        <v>14260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
         <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>21987476550</v>
+        <v>22350739360</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>52136287075</v>
+        <v>53839833450</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3095</v>
+        <v>3085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-18.77%</t>
+          <t>'-19.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F12" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>25504626411</v>
+        <v>25765190429</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
